--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92437</v>
+        <v>92450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92450</v>
+        <v>92452</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92452</v>
+        <v>92455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92455</v>
+        <v>92465</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92465</v>
+        <v>92466</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92466</v>
+        <v>92469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92469</v>
+        <v>92471</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92471</v>
+        <v>92476</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92476</v>
+        <v>92488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92488</v>
+        <v>92489</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92489</v>
+        <v>92492</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/S 216-2025 artfynd.xlsx
+++ b/artfynd/S 216-2025 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>137205346</v>
       </c>
       <c r="B65" t="n">
-        <v>92492</v>
+        <v>92496</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
